--- a/backend/local_storage/projects.xlsx
+++ b/backend/local_storage/projects.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,6 +501,78 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Santgram</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Renovora Tech</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kiran Narhari Aglawe</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>santparampra.in</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sant Parampra</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Avinash Ganesh Chate</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
